--- a/data_extactor/batch_10_fa/trimmed/batch_0008_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0008_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | زیست‌شناسی | رایانه و الکترونیک | مدیریت و امور اداری | امور اداری و دفتری</t>
+          <t>زبان انگلیسی | قانون و دولت | زیست‌شناسی | رایانه و الکترونیک | مدیریت و اداره | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران انطباق با مقررات | کارشناسان انطباق با مقررات | کارشناسان مدیریت اسناد و مدارک | بازرسان انطباق زیست‌محیطی | کارشناسان کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | مدیران امور رگولاتوری</t>
+          <t>مدیران تطبیق و نظارت مقرراتی | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان مدیریت اسناد و مدارک | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان تحلیل کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | مدیران امور انطباق مقرراتی و حقوقی صنایع</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | نگارش | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>حمل‌ونقل و ترابری | زبان انگلیسی | امور اداری و دفتری | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی | ریاضیات | اقتصاد و حسابداری</t>
+          <t>حمل و نقل | زبان انگلیسی | اداری | قانون و دولت | خدمات مشتری و شخصی | ریاضیات | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال قیاسی | درک شفاهی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک کتبی | استدلال قیاسی | درک شفاهی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کارمندان کارگزاری و ترخیص | متصدیان بار و حمل‌ونقل کالا | مأموران گمرک و حفاظت مرزی | متصدیان ارسال و خدمات فورواردری کالا | کارشناسان لجستیک | کارشناسان امور رگولاتوری و انطباق مقرراتی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کارشناسان امور اداری و معاملات کارگزاری | کارگزاران حمل‌ونقل و بار | ماموران گمرک و حفاظت مرزی | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارشناسان امور رگولاتوری و انطباق مقرراتی | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | ریاضیات | سخن گفتن | شنیدن فعال | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
+          <t>درک مطلب | ریاضیات | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ریاضیات | اقتصاد و حسابداری | رایانه و الکترونیک | مهندسی و فناوری | ساختمان‌سازی و سازه | مدیریت و امور اداری | طراحی</t>
+          <t>ریاضیات | اقتصاد و حسابداری | رایانه و الکترونیک | مهندسی و فناوری | ساختمان و ساخت‌وساز | مدیریت و اداره | طراحی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | استدلال ریاضی | درک شفاهی | مهارت کار با اعداد | درک کتبی | بیان کتبی | استدلال قیاسی</t>
+          <t>استدلال استقرایی | استدلال ریاضی | درک شفاهی | توانایی عددی | درک کتبی | بیان کتبی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | کاردان‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه ساختمانی و عمرانی | مهندسان صنایع | کارمندان برنامه‌ریزی تولید و تدارکات | کارشناسان مدیریت پروژه</t>
+          <t>نقشه‌کشان معماری و عمران | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | مهندسان صنایع | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | کارشناسان مدیریت پروژه</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | امور اداری و دفتری | مدیریت و امور اداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | آموزش و یادگیری</t>
+          <t>پرسنل و منابع انسانی | اداری | مدیریت و اداره | زبان انگلیسی | خدمات مشتری و شخصی | قانون و دولت | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران حقوق، دستمزد و مزایا | کارشناسان حقوق، مزایا و طبقه‌بندی مشاغل | کارمندان و دستیاران منابع انسانی به استثنای حقوق و دستمزد و ثبت زمان | مدیران منابع انسانی | کارشناسان روابط کار | کارمندان امور حقوق، دستمزد و ثبت ساعات کار | کارشناسان آموزش و توسعه منابع انسانی</t>
+          <t>مدیران جبران خدمت و مزایا | کارشناسان جبران خدمت، مزایا و طبقه‌بندی مشاغل | دستیاران منابع انسانی، به جز حقوق و دستمزد و ثبت ساعات کار | مدیران منابع انسانی | کارشناسان روابط کار و امور تشکل‌های کارگری | کارمندان امور حقوق، دستمزد و ثبت زمان | کارشناسان آموزش و توسعه منابع انسانی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | تفکر انتقادی</t>
+          <t>سخن گفتن | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زبان‌های خارجی | تولید محصولات غذایی و کشاورزی | ریاضیات | پرسنلی و منابع انسانی | تولید و فراوری | حقوق و مقررات دولتی</t>
+          <t>زبان خارجی | تولید مواد غذایی | ریاضیات | پرسنل و منابع انسانی | تولید و فرآوری | قانون و دولت</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | دید نزدیک</t>
+          <t>درک شفاهی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | حساسیت به مسئله | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بازرسان محصولات و امور کشاورزی | خریداران و مأموران خرید محصولات کشاورزی | کشاورزان، دامداران و سایر مدیران بخش کشاورزی | کارگران مزارع، باغات و گلخانه‌ها | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارگران ساده و جابه‌جایی دستی بار | سرپرستان رده‌اول کارگران محوطه‌سازی و باغبانی</t>
+          <t>بازرسان محصولات و فرآورده‌های کشاورزی | خریداران و کارشناسان خرید محصولات کشاورزی | مدیران امور کشاورزی، دامپروری و شیلات | کارگران زراعت، نهالستان و گلخانه | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران باغبانی، فضای سبز و نگهداری محوطه</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | درک مطلب | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | درک مطلب | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پرسنلی و منابع انسانی | زبان انگلیسی | حقوق و مقررات دولتی | مدیریت و امور اداری</t>
+          <t>پرسنل و منابع انسانی | زبان انگلیسی | قانون و دولت | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>داوران، میانجی‌گران و مصالحه‌گران حقوقی | مدیران حقوق، دستمزد و مزایا | نمایندگان و کارشناسان برابری فرصت‌های شغلی | مدیران منابع انسانی | کارشناسان منابع انسانی | روان‌شناسان صنعتی و سازمانی | وکلا</t>
+          <t>داوران، میانجی‌گران و صلح‌یاران | مدیران جبران خدمت و مزایا | کارشناسان امور انطباق و صیانت از فرصت‌های برابر استخدامی | مدیران منابع انسانی | کارشناسان منابع انسانی | روان‌شناسان صنعتی و سازمانی | وکلا</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | نگارش | استراتژی‌های یادگیری | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>حمل‌ونقل و ترابری | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | تولید و فراوری</t>
+          <t>حمل و نقل | مدیریت و اداره | خدمات مشتری و شخصی | ریاضیات | رایانه و الکترونیک | اقتصاد و حسابداری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متصدیان بار و حمل‌ونقل کالا | تحلیل‌گران لجستیک | مهندسان لجستیک | کارمندان تدارکات و کارپردازی | کارمندان برنامه‌ریزی تولید و تدارکات | مدیران تدارکات و خرید | مدیران زنجیره تأمین</t>
+          <t>کارگزاران حمل‌ونقل و بار | تحلیل‌گران لجستیک و فرایند توزیع | مهندسان لجستیک و زنجیره تأمین | کارمندان تدارکات و کارپردازی | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | مدیران خرید و تدارکات | مدیران زنجیره تامین</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نگارش | یادگیری فعال | شنیدن فعال | درک مطلب | ریاضیات | سخن گفتن | تفکر انتقادی | نظارت | استراتژی‌های یادگیری</t>
+          <t>نگارش | یادگیری فعال | گوش دادن فعال | درک مطلب | ریاضیات | سخن گفتن | تفکر انتقادی | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | حمل‌ونقل و ترابری | تولید و فراوری | رایانه و الکترونیک | اقتصاد و حسابداری | مدیریت و امور اداری</t>
+          <t>مهندسی و فناوری | ریاضیات | حمل و نقل | تولید و فرآوری | رایانه و الکترونیک | اقتصاد و حسابداری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال ریاضی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی</t>
+          <t>درک کتبی | استدلال ریاضی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | کارشناسان لجستیک | تحلیل‌گران لجستیک | تحلیل‌گران تحقیق در عملیات | مدیران زنجیره تأمین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
+          <t>کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | کارشناسان لجستیک و مدیریت زنجیره تأمین | تحلیل‌گران لجستیک و فرایند توزیع | تحلیل‌گران تحقیق در عملیات | مدیران زنجیره تامین | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نظارت | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | حمل‌ونقل و ترابری | ریاضیات | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | تولید و فراوری</t>
+          <t>رایانه و الکترونیک | حمل و نقل | ریاضیات | مدیریت و اداره | خدمات مشتری و شخصی | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | درک کتبی | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله</t>
+          <t>درک شفاهی | بیان شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری | متصدیان بار و حمل‌ونقل کالا | مهندسان صنایع | کارشناسان لجستیک | مهندسان لجستیک | کارمندان برنامه‌ریزی تولید و تدارکات | مدیران زنجیره تأمین</t>
+          <t>تحلیل‌گران هوش تجاری | کارگزاران حمل‌ونقل و بار | مهندسان صنایع | کارشناسان لجستیک و مدیریت زنجیره تأمین | مهندسان لجستیک و زنجیره تأمین | کارشناسان و کارمندان برنامه‌ریزی تولید و پیگیری امور | مدیران زنجیره تامین</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | اقتصاد و حسابداری | ریاضیات | پرسنلی و منابع انسانی | مهندسی و فناوری</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | رایانه و الکترونیک | اقتصاد و حسابداری | ریاضیات | پرسنل و منابع انسانی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مدیران سیستم‌های اطلاعاتی و فناوری اطلاعات | مدیران پروژه ساختمانی و عمرانی | مهندسان صنایع | مدیران پروژه فناوری اطلاعات | کارشناسان لجستیک | تحلیل‌گران مدیریت و فرایند</t>
+          <t>مدیران فنی و مهندسی و معماری | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پروژه‌های ساختمانی | مهندسان صنایع | مدیران پروژه‌های فناوری اطلاعات | کارشناسان لجستیک و مدیریت زنجیره تأمین | کارشناسان تحلیل مدیریت و روش‌ها</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
